--- a/etf_holdings/2026-10-14_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:52</t>
+          <t>2026-10-14 00:25:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:52</t>
+          <t>2026-10-14 00:25:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:52</t>
+          <t>2026-10-14 00:25:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:52</t>
+          <t>2026-10-14 00:25:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:52</t>
+          <t>2026-10-14 00:25:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:52</t>
+          <t>2026-10-14 00:25:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:52</t>
+          <t>2026-10-14 00:25:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:52</t>
+          <t>2026-10-14 00:25:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:52</t>
+          <t>2026-10-14 00:25:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:52</t>
+          <t>2026-10-14 00:25:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:52</t>
+          <t>2026-10-14 00:25:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:52</t>
+          <t>2026-10-14 00:25:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:52</t>
+          <t>2026-10-14 00:25:20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:52</t>
+          <t>2026-10-14 00:25:20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:52</t>
+          <t>2026-10-14 00:25:20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:53</t>
+          <t>2026-10-14 00:25:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:53</t>
+          <t>2026-10-14 00:25:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:53</t>
+          <t>2026-10-14 00:25:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:53</t>
+          <t>2026-10-14 00:25:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:53</t>
+          <t>2026-10-14 00:25:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:53</t>
+          <t>2026-10-14 00:25:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:53</t>
+          <t>2026-10-14 00:25:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:53</t>
+          <t>2026-10-14 00:25:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:53</t>
+          <t>2026-10-14 00:25:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:53</t>
+          <t>2026-10-14 00:25:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:53</t>
+          <t>2026-10-14 00:25:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:53</t>
+          <t>2026-10-14 00:25:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:53</t>
+          <t>2026-10-14 00:25:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:53</t>
+          <t>2026-10-14 00:25:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:53</t>
+          <t>2026-10-14 00:25:21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:55</t>
+          <t>2026-10-14 00:25:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:55</t>
+          <t>2026-10-14 00:25:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:55</t>
+          <t>2026-10-14 00:25:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:55</t>
+          <t>2026-10-14 00:25:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:55</t>
+          <t>2026-10-14 00:25:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:55</t>
+          <t>2026-10-14 00:25:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:55</t>
+          <t>2026-10-14 00:25:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:55</t>
+          <t>2026-10-14 00:25:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:55</t>
+          <t>2026-10-14 00:25:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:55</t>
+          <t>2026-10-14 00:25:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:55</t>
+          <t>2026-10-14 00:25:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:55</t>
+          <t>2026-10-14 00:25:22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:55</t>
+          <t>2026-10-14 00:25:22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:55</t>
+          <t>2026-10-14 00:25:22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:55</t>
+          <t>2026-10-14 00:25:22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:56</t>
+          <t>2026-10-14 00:25:24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:56</t>
+          <t>2026-10-14 00:25:24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:56</t>
+          <t>2026-10-14 00:25:24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:56</t>
+          <t>2026-10-14 00:25:24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:56</t>
+          <t>2026-10-14 00:25:24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:56</t>
+          <t>2026-10-14 00:25:24</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:56</t>
+          <t>2026-10-14 00:25:24</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:56</t>
+          <t>2026-10-14 00:25:24</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:56</t>
+          <t>2026-10-14 00:25:24</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:56</t>
+          <t>2026-10-14 00:25:24</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:56</t>
+          <t>2026-10-14 00:25:24</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">

--- a/etf_holdings/2026-10-14_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:20</t>
+          <t>2026-10-14 00:59:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:20</t>
+          <t>2026-10-14 00:59:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:20</t>
+          <t>2026-10-14 00:59:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:20</t>
+          <t>2026-10-14 00:59:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:20</t>
+          <t>2026-10-14 00:59:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:20</t>
+          <t>2026-10-14 00:59:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:20</t>
+          <t>2026-10-14 00:59:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:20</t>
+          <t>2026-10-14 00:59:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:20</t>
+          <t>2026-10-14 00:59:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:20</t>
+          <t>2026-10-14 00:59:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:20</t>
+          <t>2026-10-14 00:59:06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:20</t>
+          <t>2026-10-14 00:59:06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:20</t>
+          <t>2026-10-14 00:59:06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:20</t>
+          <t>2026-10-14 00:59:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:20</t>
+          <t>2026-10-14 00:59:06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:21</t>
+          <t>2026-10-14 00:59:17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:21</t>
+          <t>2026-10-14 00:59:17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:21</t>
+          <t>2026-10-14 00:59:17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:21</t>
+          <t>2026-10-14 00:59:17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:21</t>
+          <t>2026-10-14 00:59:17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:21</t>
+          <t>2026-10-14 00:59:17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:21</t>
+          <t>2026-10-14 00:59:17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:21</t>
+          <t>2026-10-14 00:59:17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:21</t>
+          <t>2026-10-14 00:59:17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:21</t>
+          <t>2026-10-14 00:59:17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:21</t>
+          <t>2026-10-14 00:59:17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:21</t>
+          <t>2026-10-14 00:59:17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:21</t>
+          <t>2026-10-14 00:59:17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:21</t>
+          <t>2026-10-14 00:59:17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:21</t>
+          <t>2026-10-14 00:59:17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:22</t>
+          <t>2026-10-14 00:59:28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:22</t>
+          <t>2026-10-14 00:59:28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:22</t>
+          <t>2026-10-14 00:59:28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:22</t>
+          <t>2026-10-14 00:59:28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:22</t>
+          <t>2026-10-14 00:59:28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:22</t>
+          <t>2026-10-14 00:59:28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:22</t>
+          <t>2026-10-14 00:59:28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:22</t>
+          <t>2026-10-14 00:59:28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:22</t>
+          <t>2026-10-14 00:59:28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:22</t>
+          <t>2026-10-14 00:59:28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:22</t>
+          <t>2026-10-14 00:59:28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:22</t>
+          <t>2026-10-14 00:59:28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:22</t>
+          <t>2026-10-14 00:59:28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:22</t>
+          <t>2026-10-14 00:59:28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:22</t>
+          <t>2026-10-14 00:59:28</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:24</t>
+          <t>2026-10-14 00:59:39</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:24</t>
+          <t>2026-10-14 00:59:39</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:24</t>
+          <t>2026-10-14 00:59:39</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:24</t>
+          <t>2026-10-14 00:59:39</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:24</t>
+          <t>2026-10-14 00:59:39</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:24</t>
+          <t>2026-10-14 00:59:39</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:24</t>
+          <t>2026-10-14 00:59:39</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:24</t>
+          <t>2026-10-14 00:59:39</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:24</t>
+          <t>2026-10-14 00:59:39</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:24</t>
+          <t>2026-10-14 00:59:39</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:24</t>
+          <t>2026-10-14 00:59:39</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">

--- a/etf_holdings/2026-10-14_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:06</t>
+          <t>2026-10-14 21:53:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.97%2490</t>
+          <t>0%2490</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.60%1,544,000</t>
+          <t>7.72%1,544,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.72%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:06</t>
+          <t>2026-10-14 21:53:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.16%4525</t>
+          <t>-1.1%4475</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4525</v>
+        <v>4475</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.59%736,000</t>
+          <t>6.69%736,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.59%</t>
+          <t>6.69%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:06</t>
+          <t>2026-10-14 21:53:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-4.14%556</t>
+          <t>+0.18%557</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-4.14%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.41%5,709,000</t>
+          <t>6.38%5,709,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.41%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:06</t>
+          <t>2026-10-14 21:53:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-4.27%718</t>
+          <t>+0.28%720</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-4.27%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.44%3,745,000</t>
+          <t>5.40%3,745,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.44%</t>
+          <t>5.40%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:06</t>
+          <t>2026-10-14 21:53:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.52%2195</t>
+          <t>-3.64%2115</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2195</v>
+        <v>2115</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:06</t>
+          <t>2026-10-14 21:53:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.98%2200</t>
+          <t>-0.32%923</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2200</v>
+        <v>923</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.87%845,000</t>
+          <t>3.91%2,101,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.91%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>845000</v>
+        <v>2101000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:06</t>
+          <t>2026-10-14 21:53:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.22%926</t>
+          <t>+2.27%2250</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>926</v>
+        <v>2250</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.85%2,101,000</t>
+          <t>3.73%845,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.73%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2101000</v>
+        <v>845000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:06</t>
+          <t>2026-10-14 21:53:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-9.84%5545</t>
+          <t>-5.43%6880</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.84%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5545</v>
+        <v>6880</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.68%309,000</t>
+          <t>3.67%251,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>309000</v>
+        <v>251000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:06</t>
+          <t>2026-10-14 21:53:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.91%10060</t>
+          <t>-0.55%10005</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>10060</v>
+        <v>10005</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.67%179,000</t>
+          <t>3.62%179,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>3.62%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:06</t>
+          <t>2026-10-14 21:53:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-3.1%5940</t>
+          <t>-0.93%5885</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5940</v>
+        <v>5885</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.57%301,000</t>
+          <t>3.59%301,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.59%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:06</t>
+          <t>2026-10-14 21:53:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.68%7275</t>
+          <t>+2.72%567</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7275</v>
+        <v>567</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.56%251,000</t>
+          <t>3.50%3,158,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>251000</v>
+        <v>3158000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:06</t>
+          <t>2026-10-14 21:53:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.99%552</t>
+          <t>-0.45%5520</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.99%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>552</v>
+        <v>5520</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.55%3,158,000</t>
+          <t>3.44%309,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>3158000</v>
+        <v>309000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:06</t>
+          <t>2026-10-14 21:53:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-4.92%1450</t>
+          <t>-2.76%1410</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.92%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1450</v>
+        <v>1410</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.49%1,180,000</t>
+          <t>3.44%1,180,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:06</t>
+          <t>2026-10-14 21:53:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-3.1%3280</t>
+          <t>+1.07%3315</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3280</v>
+        <v>3315</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.44%372,000</t>
+          <t>2.45%372,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:06</t>
+          <t>2026-10-14 21:53:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-8.97%1015</t>
+          <t>+0.49%1020</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.97%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.34%1,082,000</t>
+          <t>2.21%1,082,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:17</t>
+          <t>2026-10-14 21:53:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,25 +1419,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>3265台星科</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-4.17%276</t>
+          <t>+9.96%292.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-4.17%</t>
+          <t>+9.96%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>276</v>
+        <v>292.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.79%3,216,000</t>
+          <t>1.79%3,345,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1446,11 +1446,11 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>3216000</v>
+        <v>3345000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:17</t>
+          <t>2026-10-14 21:53:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3265台星科</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+1.53%266</t>
+          <t>+2.54%283</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+2.54%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.70%3,345,000</t>
+          <t>1.78%3,216,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>3345000</v>
+        <v>3216000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:17</t>
+          <t>2026-10-14 21:53:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-9.93%508</t>
+          <t>+2.95%523</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-9.93%</t>
+          <t>+2.95%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.67%1,529,000</t>
+          <t>1.56%1,529,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:17</t>
+          <t>2026-10-14 21:53:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.09%795</t>
+          <t>+7.67%856</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>+7.67%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>795</v>
+        <v>856</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.48%940,000</t>
+          <t>1.50%940,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:17</t>
+          <t>2026-10-14 21:53:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.75%141.5</t>
+          <t>+0.35%142</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>141.5</v>
+        <v>142</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.44%5,116,000</t>
+          <t>1.45%5,116,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:17</t>
+          <t>2026-10-14 21:53:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-3.04%207</t>
+          <t>+0.72%208.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-3.04%</t>
+          <t>+0.72%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>207</v>
+        <v>208.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.41%3,415,000</t>
+          <t>1.42%3,415,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:17</t>
+          <t>2026-10-14 21:53:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-4.61%1655</t>
+          <t>-0.56%714</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-4.61%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1655</v>
+        <v>714</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.40%418,000</t>
+          <t>1.39%964,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>418000</v>
+        <v>964000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:17</t>
+          <t>2026-10-14 21:53:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.42%718</t>
+          <t>+4.83%1735</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+4.83%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>718</v>
+        <v>1735</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.35%964,000</t>
+          <t>1.39%418,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>964000</v>
+        <v>418000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:17</t>
+          <t>2026-10-14 21:53:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.32%187</t>
+          <t>0%187</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.34%3,638,000</t>
+          <t>1.37%3,638,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:17</t>
+          <t>2026-10-14 21:53:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>6214精誠</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.89%740</t>
+          <t>+1.29%196</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>+1.29%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>740</v>
+        <v>196</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.29%876,000</t>
+          <t>1.34%3,438,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>876000</v>
+        <v>3438000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:17</t>
+          <t>2026-10-14 21:53:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6214精誠</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+0.26%193.5</t>
+          <t>-1.75%1685</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>193.5</v>
+        <v>1685</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.29%3,438,000</t>
+          <t>1.32%382,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>3438000</v>
+        <v>382000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:17</t>
+          <t>2026-10-14 21:53:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.29%1715</t>
+          <t>+0.95%747</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1715</v>
+        <v>747</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.27%382,000</t>
+          <t>1.30%876,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>382000</v>
+        <v>876000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:17</t>
+          <t>2026-10-14 21:53:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5425台半</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-4.68%95.8</t>
+          <t>+0.86%17500</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.68%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>95.8</v>
+        <v>17500</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.24%6,382,000</t>
+          <t>1.25%35,900</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>6382000</v>
+        <v>35900</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:17</t>
+          <t>2026-10-14 21:53:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2428興勤</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-5.51%266</t>
+          <t>+0.14%356</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.51%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>266</v>
+        <v>356</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.24%2,268,000</t>
+          <t>1.24%1,737,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,11 +2239,11 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>2268000</v>
+        <v>1737000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:17</t>
+          <t>2026-10-14 21:53:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>5425台半</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.95%17350</t>
+          <t>+1.46%97.2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>17350</v>
+        <v>97.2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.23%35,900</t>
+          <t>1.23%6,382,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>35900</v>
+        <v>6382000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:28</t>
+          <t>2026-10-14 21:53:39</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>2428興勤</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.14%355.5</t>
+          <t>+4.51%278</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+4.51%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>355.5</v>
+        <v>278</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.20%1,737,000</t>
+          <t>1.21%2,268,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1737000</v>
+        <v>2268000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:28</t>
+          <t>2026-10-14 21:53:39</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-5.96%710</t>
+          <t>+0.84%298.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.96%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>710</v>
+        <v>298.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.16%790,000</t>
+          <t>1.14%1,910,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>790000</v>
+        <v>1910000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:28</t>
+          <t>2026-10-14 21:53:39</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2467志聖</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-5.76%556</t>
+          <t>+0.14%711</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.76%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>556</v>
+        <v>711</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.14%1,000,000</t>
+          <t>1.13%790,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1000000</v>
+        <v>790000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:28</t>
+          <t>2026-10-14 21:53:39</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-2.79%296</t>
+          <t>-1.62%547</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-2.79%</t>
+          <t>-1.62%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>296</v>
+        <v>547</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.13%1,910,000</t>
+          <t>1.12%1,000,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1910000</v>
+        <v>1000000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:28</t>
+          <t>2026-10-14 21:53:39</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.62%167</t>
+          <t>+9.88%183.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2.62%</t>
+          <t>+9.88%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>167</v>
+        <v>183.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.09%3,280,000</t>
+          <t>1.10%3,280,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:28</t>
+          <t>2026-10-14 21:53:39</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.47%125</t>
+          <t>+10%137.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.47%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>125</v>
+        <v>137.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:28</t>
+          <t>2026-10-14 21:53:39</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,34 +2700,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2377微星</t>
+          <t>6472保瑞</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+1.29%157</t>
+          <t>+1.07%424.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+1.29%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>157</v>
+        <v>424.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.00%3,344,000</t>
+          <t>0.87%1,032,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>3344000</v>
+        <v>1032000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:28</t>
+          <t>2026-10-14 21:53:39</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6472保瑞</t>
+          <t>5536聖暉*</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.59%420</t>
+          <t>+1.45%908</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>420</v>
+        <v>908</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.84%1,032,000</t>
+          <t>0.82%455,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1032000</v>
+        <v>455000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:28</t>
+          <t>2026-10-14 21:53:39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-9.87%539</t>
+          <t>+9.83%592</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-9.87%</t>
+          <t>+9.83%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>539</v>
+        <v>592</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.84%729,000</t>
+          <t>0.79%729,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:28</t>
+          <t>2026-10-14 21:53:39</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5536聖暉*</t>
+          <t>2486一詮</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-3.87%895</t>
+          <t>+1.37%222.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-3.87%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>895</v>
+        <v>222.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.82%455,000</t>
+          <t>0.71%1,607,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>455000</v>
+        <v>1607000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:28</t>
+          <t>2026-10-14 21:53:39</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2486一詮</t>
+          <t>2377微星</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-6%219.5</t>
+          <t>+1.27%159</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>+1.27%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>219.5</v>
+        <v>159</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.73%1,607,000</t>
+          <t>0.53%1,672,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1607000</v>
+        <v>1672000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:28</t>
+          <t>2026-10-14 21:53:39</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.44%4,312,000</t>
+          <t>0.45%4,312,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:28</t>
+          <t>2026-10-14 21:53:39</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-2.44%641</t>
+          <t>+2.34%656</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-2.44%</t>
+          <t>+2.34%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:28</t>
+          <t>2026-10-14 21:53:39</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6640均華</t>
+          <t>3617碩天</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-6.49%1080</t>
+          <t>+3.46%269</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-6.49%</t>
+          <t>+3.46%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1080</v>
+        <v>269</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.32%143,000</t>
+          <t>0.33%627,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>143000</v>
+        <v>627000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:28</t>
+          <t>2026-10-14 21:53:39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.17%127</t>
+          <t>-0.39%126.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>127</v>
+        <v>126.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.32%1,281,000</t>
+          <t>0.33%1,281,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:39</t>
+          <t>2026-10-14 21:53:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,25 +3249,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3617碩天</t>
+          <t>2885元大金</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.58%260</t>
+          <t>+2.27%72.2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>260</v>
+        <v>72.2</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.31%627,000</t>
+          <t>0.31%2,213,556</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3276,11 +3276,11 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>627000</v>
+        <v>2213556</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:39</t>
+          <t>2026-10-14 21:53:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2885元大金</t>
+          <t>6640均華</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.71%70.6</t>
+          <t>-0.93%1070</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>70.59999999999999</v>
+        <v>1070</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.30%2,213,556</t>
+          <t>0.31%143,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>2213556</v>
+        <v>143000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:39</t>
+          <t>2026-10-14 21:53:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.69%1165</t>
+          <t>+2.15%1190</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>+2.15%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1165</v>
+        <v>1190</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:39</t>
+          <t>2026-10-14 21:53:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-1.29%46</t>
+          <t>-0.65%45.7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>46</v>
+        <v>45.7</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:39</t>
+          <t>2026-10-14 21:53:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.06%8095</t>
+          <t>+1.85%8245</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>8095</v>
+        <v>8245</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:39</t>
+          <t>2026-10-14 21:53:41</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-1.4%2810</t>
+          <t>+2.31%2875</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+2.31%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2810</v>
+        <v>2875</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:39</t>
+          <t>2026-10-14 21:53:41</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,16 +3620,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-1.49%165</t>
+          <t>+1.82%168</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:39</t>
+          <t>2026-10-14 21:53:41</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3681,16 +3681,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-5.56%493</t>
+          <t>+1.83%502</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:39</t>
+          <t>2026-10-14 21:53:41</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3742,16 +3742,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-8.43%663</t>
+          <t>+4.07%690</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-8.43%</t>
+          <t>+4.07%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>663</v>
+        <v>690</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:39</t>
+          <t>2026-10-14 21:53:41</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3803,25 +3803,25 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>+1.8%50.9</t>
+          <t>+0.39%51.1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-14 00:59:39</t>
+          <t>2026-10-14 21:53:41</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3864,16 +3864,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>+0.95%160</t>
+          <t>+0.31%160.5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>160</v>
+        <v>160.5</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-14_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:37</t>
+          <t>2026-10-14 22:01:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:37</t>
+          <t>2026-10-14 22:01:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:37</t>
+          <t>2026-10-14 22:01:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:37</t>
+          <t>2026-10-14 22:01:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:37</t>
+          <t>2026-10-14 22:01:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:37</t>
+          <t>2026-10-14 22:01:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:37</t>
+          <t>2026-10-14 22:01:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:37</t>
+          <t>2026-10-14 22:01:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:37</t>
+          <t>2026-10-14 22:01:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:37</t>
+          <t>2026-10-14 22:01:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:37</t>
+          <t>2026-10-14 22:01:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:37</t>
+          <t>2026-10-14 22:01:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:37</t>
+          <t>2026-10-14 22:01:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:37</t>
+          <t>2026-10-14 22:01:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:37</t>
+          <t>2026-10-14 22:01:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:38</t>
+          <t>2026-10-14 22:01:18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:38</t>
+          <t>2026-10-14 22:01:18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:38</t>
+          <t>2026-10-14 22:01:18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:38</t>
+          <t>2026-10-14 22:01:18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:38</t>
+          <t>2026-10-14 22:01:18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:38</t>
+          <t>2026-10-14 22:01:18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:38</t>
+          <t>2026-10-14 22:01:18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:38</t>
+          <t>2026-10-14 22:01:18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:38</t>
+          <t>2026-10-14 22:01:18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:38</t>
+          <t>2026-10-14 22:01:18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:38</t>
+          <t>2026-10-14 22:01:18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:38</t>
+          <t>2026-10-14 22:01:18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:38</t>
+          <t>2026-10-14 22:01:18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:38</t>
+          <t>2026-10-14 22:01:18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:38</t>
+          <t>2026-10-14 22:01:18</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:39</t>
+          <t>2026-10-14 22:01:20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:39</t>
+          <t>2026-10-14 22:01:20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:39</t>
+          <t>2026-10-14 22:01:20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:39</t>
+          <t>2026-10-14 22:01:20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:39</t>
+          <t>2026-10-14 22:01:20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:39</t>
+          <t>2026-10-14 22:01:20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:39</t>
+          <t>2026-10-14 22:01:20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:39</t>
+          <t>2026-10-14 22:01:20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:39</t>
+          <t>2026-10-14 22:01:20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:39</t>
+          <t>2026-10-14 22:01:20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:39</t>
+          <t>2026-10-14 22:01:20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:39</t>
+          <t>2026-10-14 22:01:20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:39</t>
+          <t>2026-10-14 22:01:20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:39</t>
+          <t>2026-10-14 22:01:20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:39</t>
+          <t>2026-10-14 22:01:20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:41</t>
+          <t>2026-10-14 22:01:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:41</t>
+          <t>2026-10-14 22:01:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:41</t>
+          <t>2026-10-14 22:01:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:41</t>
+          <t>2026-10-14 22:01:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:41</t>
+          <t>2026-10-14 22:01:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:41</t>
+          <t>2026-10-14 22:01:21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:41</t>
+          <t>2026-10-14 22:01:21</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:41</t>
+          <t>2026-10-14 22:01:21</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:41</t>
+          <t>2026-10-14 22:01:21</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:41</t>
+          <t>2026-10-14 22:01:21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:41</t>
+          <t>2026-10-14 22:01:21</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">

--- a/etf_holdings/2026-10-14_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:17</t>
+          <t>2026-10-14 22:31:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:17</t>
+          <t>2026-10-14 22:31:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:17</t>
+          <t>2026-10-14 22:31:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:17</t>
+          <t>2026-10-14 22:31:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:17</t>
+          <t>2026-10-14 22:31:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:17</t>
+          <t>2026-10-14 22:31:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:17</t>
+          <t>2026-10-14 22:31:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:17</t>
+          <t>2026-10-14 22:31:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:17</t>
+          <t>2026-10-14 22:31:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:17</t>
+          <t>2026-10-14 22:31:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:17</t>
+          <t>2026-10-14 22:31:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:17</t>
+          <t>2026-10-14 22:31:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:17</t>
+          <t>2026-10-14 22:31:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:17</t>
+          <t>2026-10-14 22:31:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:17</t>
+          <t>2026-10-14 22:31:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:18</t>
+          <t>2026-10-14 22:31:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:18</t>
+          <t>2026-10-14 22:31:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:18</t>
+          <t>2026-10-14 22:31:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:18</t>
+          <t>2026-10-14 22:31:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:18</t>
+          <t>2026-10-14 22:31:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:18</t>
+          <t>2026-10-14 22:31:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:18</t>
+          <t>2026-10-14 22:31:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:18</t>
+          <t>2026-10-14 22:31:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:18</t>
+          <t>2026-10-14 22:31:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:18</t>
+          <t>2026-10-14 22:31:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:18</t>
+          <t>2026-10-14 22:31:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:18</t>
+          <t>2026-10-14 22:31:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:18</t>
+          <t>2026-10-14 22:31:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:18</t>
+          <t>2026-10-14 22:31:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:18</t>
+          <t>2026-10-14 22:31:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:20</t>
+          <t>2026-10-14 22:31:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:20</t>
+          <t>2026-10-14 22:31:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:20</t>
+          <t>2026-10-14 22:31:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:20</t>
+          <t>2026-10-14 22:31:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:20</t>
+          <t>2026-10-14 22:31:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:20</t>
+          <t>2026-10-14 22:31:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:20</t>
+          <t>2026-10-14 22:31:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:20</t>
+          <t>2026-10-14 22:31:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:20</t>
+          <t>2026-10-14 22:31:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:20</t>
+          <t>2026-10-14 22:31:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:20</t>
+          <t>2026-10-14 22:31:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:20</t>
+          <t>2026-10-14 22:31:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:20</t>
+          <t>2026-10-14 22:31:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:20</t>
+          <t>2026-10-14 22:31:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:20</t>
+          <t>2026-10-14 22:31:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:21</t>
+          <t>2026-10-14 22:31:25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:21</t>
+          <t>2026-10-14 22:31:25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:21</t>
+          <t>2026-10-14 22:31:25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:21</t>
+          <t>2026-10-14 22:31:25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:21</t>
+          <t>2026-10-14 22:31:25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:21</t>
+          <t>2026-10-14 22:31:25</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:21</t>
+          <t>2026-10-14 22:31:25</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:21</t>
+          <t>2026-10-14 22:31:25</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:21</t>
+          <t>2026-10-14 22:31:25</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:21</t>
+          <t>2026-10-14 22:31:25</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:21</t>
+          <t>2026-10-14 22:31:25</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
